--- a/data/trans_dic/P57_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Habitat-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,58; 33,74</t>
+          <t>26,62; 33,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,02; 46,92</t>
+          <t>38,12; 47,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,23; 29,47</t>
+          <t>23,28; 29,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,97; 43,29</t>
+          <t>37,3; 43,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,61; 30,65</t>
+          <t>25,78; 30,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,9; 44,21</t>
+          <t>38,91; 44,09</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,4; 32,43</t>
+          <t>26,55; 32,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,09; 77,99</t>
+          <t>48,37; 79,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,8; 29,27</t>
+          <t>23,48; 29,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,38; 44,99</t>
+          <t>39,33; 45,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,12; 29,94</t>
+          <t>25,79; 29,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,2; 67,97</t>
+          <t>45,22; 69,93</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,85; 33,79</t>
+          <t>26,92; 33,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,21; 58,49</t>
+          <t>50,6; 58,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,51; 28,98</t>
+          <t>22,5; 28,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 48,34</t>
+          <t>19,2; 48,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,48; 30,0</t>
+          <t>25,46; 30,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,16; 51,82</t>
+          <t>27,77; 51,68</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 35,24</t>
+          <t>29,05; 34,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,77; 44,93</t>
+          <t>37,76; 44,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,99; 29,53</t>
+          <t>23,98; 29,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,69; 37,61</t>
+          <t>27,27; 37,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 31,43</t>
+          <t>27,16; 31,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,08; 39,91</t>
+          <t>33,37; 40,12</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,9; 32,18</t>
+          <t>28,92; 32,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,31; 62,22</t>
+          <t>46,32; 61,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,88; 27,82</t>
+          <t>24,88; 27,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,84; 41,11</t>
+          <t>30,17; 40,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,15; 29,37</t>
+          <t>27,22; 29,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,66; 50,15</t>
+          <t>40,55; 50,22</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>177957; 225874</t>
+          <t>178245; 226061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>238992; 294960</t>
+          <t>239648; 295651</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155019; 196699</t>
+          <t>155361; 199002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>247811; 290156</t>
+          <t>249991; 290294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>342326; 409813</t>
+          <t>344680; 412268</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>505291; 574280</t>
+          <t>505380; 572669</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>269587; 331173</t>
+          <t>271139; 332905</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>573025; 929244</t>
+          <t>576343; 947872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247931; 305019</t>
+          <t>244648; 305485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>373970; 427332</t>
+          <t>373498; 428954</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>539006; 617742</t>
+          <t>532097; 616288</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>967933; 1455433</t>
+          <t>968336; 1497473</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>203123; 255594</t>
+          <t>203617; 253376</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>353839; 412136</t>
+          <t>356589; 414028</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175400; 225812</t>
+          <t>175356; 222401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179655; 449351</t>
+          <t>178497; 449726</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>391293; 460647</t>
+          <t>391016; 462673</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>427563; 846887</t>
+          <t>453826; 844556</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>272701; 328930</t>
+          <t>271200; 323922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>349310; 415559</t>
+          <t>349174; 413701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249378; 306980</t>
+          <t>249316; 309195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>302012; 410303</t>
+          <t>297458; 408269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>541688; 620107</t>
+          <t>535938; 620546</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>666760; 804386</t>
+          <t>672675; 808724</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>977133; 1087918</t>
+          <t>977737; 1087075</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1597551; 2146360</t>
+          <t>1598032; 2134364</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>877663; 981482</t>
+          <t>877838; 976656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1122807; 1496713</t>
+          <t>1098223; 1489538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1875864; 2028846</t>
+          <t>1880581; 2033723</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2883072; 3555898</t>
+          <t>2875021; 3560702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,62; 33,77</t>
+          <t>26,21; 33,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,12; 47,03</t>
+          <t>37,81; 46,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 29,82</t>
+          <t>22,99; 29,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,3; 43,31</t>
+          <t>36,99; 43,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,78; 30,84</t>
+          <t>25,77; 30,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,91; 44,09</t>
+          <t>38,42; 43,59</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,55; 32,6</t>
+          <t>26,39; 32,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,37; 79,55</t>
+          <t>45,44; 52,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,48; 29,32</t>
+          <t>23,74; 29,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,33; 45,16</t>
+          <t>38,84; 44,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,79; 29,87</t>
+          <t>25,82; 29,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,22; 69,93</t>
+          <t>42,94; 47,31</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 33,5</t>
+          <t>26,5; 33,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,6; 58,75</t>
+          <t>49,57; 58,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,5; 28,54</t>
+          <t>22,32; 28,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,2; 48,38</t>
+          <t>45,61; 52,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,46; 30,13</t>
+          <t>25,52; 30,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,77; 51,68</t>
+          <t>48,62; 53,93</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 34,7</t>
+          <t>29,05; 35,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,76; 44,73</t>
+          <t>37,57; 44,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,98; 29,75</t>
+          <t>23,98; 29,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,27; 37,43</t>
+          <t>33,61; 38,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,16; 31,45</t>
+          <t>27,17; 31,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,37; 40,12</t>
+          <t>36,37; 40,64</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,92; 32,15</t>
+          <t>28,83; 31,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,32; 61,87</t>
+          <t>44,43; 48,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,88; 27,68</t>
+          <t>24,87; 28,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,17; 40,92</t>
+          <t>39,66; 42,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,22; 29,44</t>
+          <t>27,24; 29,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,55; 50,22</t>
+          <t>42,54; 44,93</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266842</t>
+          <t>287114</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270726</t>
+          <t>290667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>537568</t>
+          <t>577781</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>178245; 226061</t>
+          <t>175492; 225573</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>239648; 295651</t>
+          <t>258387; 314410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155361; 199002</t>
+          <t>153435; 198237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>249991; 290294</t>
+          <t>268860; 313305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>344680; 412268</t>
+          <t>344473; 412634</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>505380; 572669</t>
+          <t>541756; 614627</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>713006</t>
+          <t>513180</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402187</t>
+          <t>442968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1115192</t>
+          <t>956149</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>271139; 332905</t>
+          <t>269513; 329785</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>576343; 947872</t>
+          <t>476007; 549159</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244648; 305485</t>
+          <t>247357; 303919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>373498; 428954</t>
+          <t>412937; 472696</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>532097; 616288</t>
+          <t>532666; 616922</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>968336; 1497473</t>
+          <t>906166; 998375</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>384706</t>
+          <t>429625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337565</t>
+          <t>395424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>722272</t>
+          <t>825048</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>203617; 253376</t>
+          <t>200429; 251231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>356589; 414028</t>
+          <t>398099; 466853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175356; 222401</t>
+          <t>173945; 222268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178497; 449726</t>
+          <t>368540; 421950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>391016; 462673</t>
+          <t>391908; 464774</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>453826; 844556</t>
+          <t>783306; 868955</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>382590</t>
+          <t>404465</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370905</t>
+          <t>402018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>753495</t>
+          <t>806483</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>271200; 323922</t>
+          <t>271184; 328746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>349174; 413701</t>
+          <t>371138; 439865</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249316; 309195</t>
+          <t>249257; 307235</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>297458; 408269</t>
+          <t>374621; 432627</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>535938; 620546</t>
+          <t>535969; 617569</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>672675; 808724</t>
+          <t>764666; 854510</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1747144</t>
+          <t>1634384</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1381383</t>
+          <t>1531076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3128528</t>
+          <t>3165460</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>977737; 1087075</t>
+          <t>974570; 1080195</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1598032; 2134364</t>
+          <t>1564810; 1698228</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>877838; 976656</t>
+          <t>877364; 988351</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1098223; 1489538</t>
+          <t>1472474; 1587964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1880581; 2033723</t>
+          <t>1881644; 2035801</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2875021; 3560702</t>
+          <t>3077618; 3250344</t>
         </is>
       </c>
     </row>
